--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -10,6 +10,7 @@
     <sheet name="IndustryType" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="GlobalRarity" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CurrencyType" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="GachaRewardType" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -1080,4 +1081,104 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>아이템 — GachaItemTable</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 — GachaCharacterTable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -70,8 +70,23 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +111,21 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -109,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -142,6 +172,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,53 +597,58 @@
   </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -599,12 +658,12 @@
       <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>농사</t>
         </is>
@@ -614,12 +673,12 @@
       <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>낚시</t>
         </is>
@@ -629,12 +688,12 @@
       <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>채광</t>
         </is>
@@ -644,12 +703,12 @@
       <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>벌목</t>
         </is>
@@ -659,12 +718,12 @@
       <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>사냥</t>
         </is>
@@ -674,12 +733,12 @@
       <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -689,12 +748,12 @@
       <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>특수</t>
         </is>
@@ -713,53 +772,58 @@
   </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -769,12 +833,12 @@
       <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>농사</t>
         </is>
@@ -784,12 +848,12 @@
       <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>낚시</t>
         </is>
@@ -799,12 +863,12 @@
       <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>채광</t>
         </is>
@@ -814,12 +878,12 @@
       <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>벌목</t>
         </is>
@@ -829,12 +893,12 @@
       <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>사냥</t>
         </is>
@@ -854,57 +918,59 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="19.109375" customWidth="1" min="4" max="4"/>
     <col width="21.6640625" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -914,12 +980,12 @@
       <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>일반, 흰색/회색 #9D9D9D</t>
         </is>
@@ -929,12 +995,12 @@
       <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>고급, 초록 #1EFF00</t>
         </is>
@@ -944,12 +1010,12 @@
       <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>희귀, 파랑 #0070DD</t>
         </is>
@@ -959,12 +1025,12 @@
       <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>영웅, 보라 #A335EE</t>
         </is>
@@ -974,12 +1040,12 @@
       <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>전설, 주황/금색 #FF8000</t>
         </is>
@@ -989,12 +1055,12 @@
       <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>신화, 빨강/핑크 #E6CC80</t>
         </is>
@@ -1013,53 +1079,58 @@
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1069,27 +1140,27 @@
       <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>골드</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>다이아</t>
         </is>
@@ -1109,57 +1180,57 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1169,12 +1240,12 @@
       <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>아이템 — GachaItemTable</t>
         </is>
@@ -1184,12 +1255,12 @@
       <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Character</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>캐릭터 — GachaCharacterTable</t>
         </is>
@@ -1208,98 +1279,103 @@
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>무기</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Accessory</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>장신구</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>보석</t>
         </is>
@@ -1318,113 +1394,118 @@
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>무기 칸</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Accessory1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>장신구 칸 1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Accessory2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>장신구 칸 2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>보석 칸</t>
         </is>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="15">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -85,8 +85,63 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +181,21 @@
         <fgColor theme="2" tint="-0.1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF595959"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0D0D0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -139,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,6 +266,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -604,156 +701,156 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>농사</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>낚시</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>채광</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>벌목</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>사냥</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>특수</t>
         </is>
@@ -779,126 +876,126 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>농사</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>낚시</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>채광</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>벌목</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>사냥</t>
         </is>
@@ -926,141 +1023,141 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>일반, 흰색/회색 #9D9D9D</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>고급, 초록 #1EFF00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>희귀, 파랑 #0070DD</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>영웅, 보라 #A335EE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>전설, 주황/금색 #FF8000</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>신화, 빨강/핑크 #E6CC80</t>
         </is>
@@ -1086,81 +1183,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>골드</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>다이아</t>
         </is>
@@ -1186,81 +1283,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>아이템 — GachaItemTable</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Character</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>캐릭터 — GachaCharacterTable</t>
         </is>
@@ -1286,96 +1383,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>무기</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Accessory</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>장신구</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>보석</t>
         </is>
@@ -1401,111 +1498,111 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>EID</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>EnumID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>무기 칸</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Accessory1</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>장신구 칸 1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Accessory2</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>장신구 칸 2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>보석 칸</t>
         </is>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -13,6 +13,7 @@
     <sheet name="GachaRewardType" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="EquipKind" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="EquipSlot" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="UserTraitEffect" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1274,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1360,6 +1361,21 @@
       <c r="C5" s="25" t="inlineStr">
         <is>
           <t>캐릭터 — GachaCharacterTable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>장비 — GachaEquipTable</t>
         </is>
       </c>
     </row>
@@ -1611,4 +1627,89 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>작업속도 가산 — EffectValue 천분율, Industry None=전 산업</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1275,12 +1275,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1376,6 +1376,21 @@
       <c r="C6" s="25" t="inlineStr">
         <is>
           <t>장비 — GachaEquipTable</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>골드 — GachaGoldTable (구간 MinAmount~MaxAmount)</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -14,6 +14,8 @@
     <sheet name="EquipKind" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="EquipSlot" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="UserTraitEffect" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="EnchantOptionType" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="EnchantAction" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -862,6 +864,121 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>인챈트 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>GradeUp</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>등급 상승 판정 + 줄 재롤</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>ExpandLine</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>인챈트 줄 3줄로 확장</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1727,4 +1844,104 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>작업속도 가산 — Value 천분율, Industry None=전 산업</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>CharacterExp</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>캐릭터 경험치 가산 — Value 천분율</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1292,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,21 +1363,6 @@
       <c r="C4" s="25" t="inlineStr">
         <is>
           <t>골드</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>Dia</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>다이아</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -15,7 +15,6 @@
     <sheet name="EquipSlot" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="UserTraitEffect" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="EnchantOptionType" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="EnchantAction" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -864,121 +863,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>EID</t>
-        </is>
-      </c>
-      <c r="B1" s="26" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="26" t="inlineStr">
-        <is>
-          <t>Desc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>EnumID</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>인챈트 부여</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>GradeUp</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>등급 상승 판정 + 줄 재롤</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>ExpandLine</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
-        <is>
-          <t>인챈트 줄 3줄로 확장</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1636,12 +1636,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1707,6 +1707,36 @@
       <c r="C4" s="25" t="inlineStr">
         <is>
           <t>작업속도 가산 — EffectValue 천분율, Industry None=전 산업</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>IndustryUnlock</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>산업 개척 — 특성 레벨 N이면 그 산업 Lv N까지 열린다 (기본 레벨 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>산출량 가산 — 레벨당 EffectValue 천분율, Industry None=전 산업</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -698,7 +698,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -774,12 +774,12 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>유적 발굴</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -949,12 +949,12 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>낚시</t>
+          <t>유적 발굴</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1014,12 +1014,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="19.109375" customWidth="1" min="4" max="4"/>
     <col width="21.6640625" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1162,6 +1162,21 @@
       <c r="C9" s="25" t="inlineStr">
         <is>
           <t>신화, 빨강/핑크 #E6CC80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>스페셜, 무지개 (공용 최상위 · 유물·아티팩트 — T-150)</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -694,12 +694,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,7 +854,37 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>특수</t>
+          <t>사용 안 함 (2026-10-12 상자·소모품을 Box·Consumable로 옮김 — 등급 Special과 겹침)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>상자</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>소모품</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1681,11 +1681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1782,6 +1782,36 @@
       <c r="C6" s="25" t="inlineStr">
         <is>
           <t>산출량 가산 — 레벨당 EffectValue 천분율, Industry None=전 산업</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>AppraiseCostDiscount</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>감정 비용 할인 — EffectValue 천분율, 합계 500‰까지 (아티팩트 전용 — T-150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>RelicChanceAdd</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>유물 발견 확률 — EffectValue 천분율, 유물 롤 확률에 곱한다 (아티팩트 전용 — T-150)</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -885,6 +885,21 @@
       <c r="C12" s="25" t="inlineStr">
         <is>
           <t>소모품</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>미감정 유물 — 골드로 감정(OpenCostGold)하면 OpenGachaId 풀을 돈다 (T-150)</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1321,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1422,6 +1437,21 @@
       <c r="C7" s="25" t="inlineStr">
         <is>
           <t>골드 — GachaGoldTable (구간 MinAmount~MaxAmount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Artifact</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>아티팩트 — GachaArtifactTable · 인벤토리가 아닌 아티팩트 보관함으로 (T-150)</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -15,6 +15,7 @@
     <sheet name="EquipSlot" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="UserTraitEffect" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="EnchantOptionType" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="BuildingEffectType" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -908,6 +909,106 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>작업속도 가산 — EffectValue 천분율, 그 건물의 산업에만</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>산출량 가산 — EffectValue 천분율, 그 건물의 산업에만</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -16,6 +16,7 @@
     <sheet name="UserTraitEffect" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="EnchantOptionType" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="BuildingEffectType" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="CharacterRace" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1009,6 +1010,138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="19.109375" customWidth="1" min="4" max="4"/>
+    <col width="21.6640625" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>인간</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>마물</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>언데드</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Golem</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>골렘</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -15,8 +15,7 @@
     <sheet name="EquipSlot" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="UserTraitEffect" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="EnchantOptionType" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="BuildingEffectType" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="CharacterRace" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CharacterRace" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -916,106 +915,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>EID</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>Desc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>EnumID</t>
-        </is>
-      </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C2" s="21" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>작업속도 가산 — EffectValue 천분율, 그 건물의 산업에만</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>YieldAdd</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>산출량 가산 — EffectValue 천분율, 그 건물의 산업에만</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
